--- a/po.xlsx
+++ b/po.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -147,8 +147,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AxTable1" displayName="AxTable1" ref="A1:T1011" headerRowCount="1">
-  <autoFilter ref="A1:T1011"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AxTable1" displayName="AxTable1" ref="A1:T1017" headerRowCount="1">
+  <autoFilter ref="A1:T1017"/>
   <tableColumns count="20">
     <tableColumn id="1" name="Purchase order"/>
     <tableColumn id="2" name="Vendor account"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1011"/>
+  <dimension ref="A1:T1017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -30705,16 +30705,16 @@
       </c>
       <c r="Q414" t="inlineStr">
         <is>
-          <t>arman.b</t>
+          <t>not recorded</t>
         </is>
       </c>
       <c r="R414" t="inlineStr">
         <is>
-          <t>Procurement Manager</t>
+          <t>LPO sent/shared with supplier</t>
         </is>
       </c>
       <c r="S414" s="5" t="n">
-        <v>46274.56513888889</v>
+        <v>46275.5</v>
       </c>
     </row>
     <row r="415">
@@ -42622,7 +42622,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>Backorder</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -42665,7 +42665,7 @@
         </is>
       </c>
       <c r="S578" s="5" t="n">
-        <v>46127.5</v>
+        <v>46275.5</v>
       </c>
     </row>
     <row r="579">
@@ -70488,7 +70488,7 @@
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G958" t="inlineStr">
@@ -70532,11 +70532,11 @@
       </c>
       <c r="R958" t="inlineStr">
         <is>
-          <t>Procurement Manager</t>
+          <t>LPO sent/shared with supplier</t>
         </is>
       </c>
       <c r="S958" s="5" t="n">
-        <v>46275.25003472222</v>
+        <v>46275.5</v>
       </c>
     </row>
     <row r="959">
@@ -71376,7 +71376,7 @@
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G970" t="inlineStr">
@@ -71420,8 +71420,11 @@
       </c>
       <c r="R970" t="inlineStr">
         <is>
-          <t>Procurement Manager</t>
-        </is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S970" s="5" t="n">
+        <v>46275.5</v>
       </c>
     </row>
     <row r="971">
@@ -71447,7 +71450,7 @@
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G971" t="inlineStr">
@@ -71491,8 +71494,11 @@
       </c>
       <c r="R971" t="inlineStr">
         <is>
-          <t>Procurement Manager</t>
-        </is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S971" s="5" t="n">
+        <v>46275.5</v>
       </c>
     </row>
     <row r="972">
@@ -71518,7 +71524,7 @@
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G972" t="inlineStr">
@@ -71562,8 +71568,11 @@
       </c>
       <c r="R972" t="inlineStr">
         <is>
-          <t>Procurement Manager</t>
-        </is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S972" s="5" t="n">
+        <v>46275.5</v>
       </c>
     </row>
     <row r="973">
@@ -71737,7 +71746,7 @@
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t>InReview</t>
+          <t>Draft</t>
         </is>
       </c>
       <c r="G975" t="inlineStr">
@@ -71776,7 +71785,7 @@
       </c>
       <c r="Q975" t="inlineStr">
         <is>
-          <t>Riyaz.n</t>
+          <t>not recorded</t>
         </is>
       </c>
       <c r="R975" t="inlineStr">
@@ -71785,7 +71794,7 @@
         </is>
       </c>
       <c r="S975" s="5" t="n">
-        <v>46274.57559027777</v>
+        <v>46275.36559027778</v>
       </c>
     </row>
     <row r="976">
@@ -71939,22 +71948,22 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>SCPG-PO2600002</t>
+          <t>SCBM-PO2601634</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>VEND-00224</t>
+          <t>VEND-00031</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>VEND-00224</t>
+          <t>VEND-00031</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>Asaleeb Technology</t>
+          <t>Burhani Trading LLC</t>
         </is>
       </c>
       <c r="F978" t="inlineStr">
@@ -71973,27 +71982,27 @@
         </is>
       </c>
       <c r="I978" s="5" t="n">
-        <v>46031.5</v>
+        <v>46275.5</v>
       </c>
       <c r="J978" s="5" t="n">
-        <v>46031.5</v>
+        <v>46275.5</v>
       </c>
       <c r="M978" t="n">
-        <v>2040</v>
+        <v>835</v>
       </c>
       <c r="N978" t="inlineStr">
         <is>
-          <t>Concierge Services</t>
+          <t>Home Maintenance Services</t>
         </is>
       </c>
       <c r="O978" t="inlineStr">
         <is>
-          <t>NORTH RESIDENCE</t>
+          <t>AL TAMR</t>
         </is>
       </c>
       <c r="P978" t="inlineStr">
         <is>
-          <t>Contracted</t>
+          <t>Variation</t>
         </is>
       </c>
       <c r="Q978" t="inlineStr">
@@ -72007,33 +72016,33 @@
         </is>
       </c>
       <c r="S978" s="5" t="n">
-        <v>46037.5</v>
+        <v>46275.5</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>SCPG-PO2600004</t>
+          <t>SCBM-PO2601635</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>VEND-00224</t>
+          <t>VEND-00031</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>VEND-00224</t>
+          <t>VEND-00031</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>Asaleeb Technology</t>
+          <t>Burhani Trading LLC</t>
         </is>
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>InReview</t>
         </is>
       </c>
       <c r="G979" t="inlineStr">
@@ -72047,22 +72056,22 @@
         </is>
       </c>
       <c r="I979" s="5" t="n">
-        <v>46042.5</v>
+        <v>46275.5</v>
       </c>
       <c r="J979" s="5" t="n">
-        <v>46042.5</v>
+        <v>46275.5</v>
       </c>
       <c r="M979" t="n">
-        <v>2040</v>
+        <v>690</v>
       </c>
       <c r="N979" t="inlineStr">
         <is>
-          <t>Accomodation Services</t>
+          <t>Building Services</t>
         </is>
       </c>
       <c r="O979" t="inlineStr">
         <is>
-          <t>Al Rams</t>
+          <t>MAG 318</t>
         </is>
       </c>
       <c r="P979" t="inlineStr">
@@ -72072,47 +72081,47 @@
       </c>
       <c r="Q979" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>arman.b</t>
         </is>
       </c>
       <c r="R979" t="inlineStr">
         <is>
-          <t>LPO sent/shared with supplier</t>
+          <t>Accounting Manager</t>
         </is>
       </c>
       <c r="S979" s="5" t="n">
-        <v>46048.5</v>
+        <v>46275.33657407408</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>SCPG-PO2600005</t>
+          <t>SCBM-PO2601636</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>VEND-02528</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>VEND-02528</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>AL JABER SECURITY COMPANY L.L.C</t>
+          <t>Arasca Medical Equipment Trading LLC</t>
         </is>
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>InReview</t>
         </is>
       </c>
       <c r="G980" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Backorder</t>
         </is>
       </c>
       <c r="H980" t="inlineStr">
@@ -72121,67 +72130,57 @@
         </is>
       </c>
       <c r="I980" s="5" t="n">
-        <v>46048.5</v>
+        <v>46275.5</v>
       </c>
       <c r="J980" s="5" t="n">
-        <v>46048.5</v>
+        <v>46275.5</v>
       </c>
       <c r="M980" t="n">
-        <v>52800</v>
+        <v>3450</v>
       </c>
       <c r="N980" t="inlineStr">
         <is>
-          <t>Security Services</t>
-        </is>
-      </c>
-      <c r="O980" t="inlineStr">
-        <is>
-          <t>AL layyah</t>
-        </is>
-      </c>
-      <c r="P980" t="inlineStr">
-        <is>
-          <t>Contracted</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="Q980" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>Riyaz.n</t>
         </is>
       </c>
       <c r="R980" t="inlineStr">
         <is>
-          <t>LPO sent/shared with supplier</t>
+          <t>Procurement Manager</t>
         </is>
       </c>
       <c r="S980" s="5" t="n">
-        <v>46080.5</v>
+        <v>46275.35538194444</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>SCPG-PO2600006</t>
+          <t>SCBM-PO2601638</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>VEND-00465</t>
+          <t>VEND-00224</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>VEND-00465</t>
+          <t>VEND-00224</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>Fouress (Middle East) Safety Products FZC</t>
+          <t>Asaleeb Technology</t>
         </is>
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>InReview</t>
         </is>
       </c>
       <c r="G981" t="inlineStr">
@@ -72195,67 +72194,54 @@
         </is>
       </c>
       <c r="I981" s="5" t="n">
-        <v>46050.5</v>
+        <v>46275.5</v>
       </c>
       <c r="J981" s="5" t="n">
-        <v>46050.5</v>
+        <v>46275.5</v>
       </c>
       <c r="M981" t="n">
-        <v>210</v>
+        <v>7430</v>
       </c>
       <c r="N981" t="inlineStr">
         <is>
-          <t>Security Services</t>
-        </is>
-      </c>
-      <c r="O981" t="inlineStr">
-        <is>
-          <t>THE CREEKSIDE MGALLERY HOTEL</t>
-        </is>
-      </c>
-      <c r="P981" t="inlineStr">
-        <is>
-          <t>Contracted</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="Q981" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>Riyaz.n</t>
         </is>
       </c>
       <c r="R981" t="inlineStr">
         <is>
-          <t>LPO sent/shared with supplier</t>
-        </is>
-      </c>
-      <c r="S981" s="5" t="n">
-        <v>46052.5</v>
+          <t>Procurement Manager</t>
+        </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>SCPG-PO2600009</t>
+          <t>SCBM-PO2601639</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>VEND-00224</t>
+          <t>VEND-00678</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>VEND-00224</t>
+          <t>VEND-00678</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>Asaleeb Technology</t>
+          <t>MEDIA EDGE ADVERTISING &amp; GIFTS LLC</t>
         </is>
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>InReview</t>
         </is>
       </c>
       <c r="G982" t="inlineStr">
@@ -72269,22 +72255,22 @@
         </is>
       </c>
       <c r="I982" s="5" t="n">
-        <v>46052.5</v>
+        <v>46275.5</v>
       </c>
       <c r="J982" s="5" t="n">
-        <v>46052.5</v>
+        <v>46275.5</v>
       </c>
       <c r="M982" t="n">
-        <v>1170</v>
+        <v>400</v>
       </c>
       <c r="N982" t="inlineStr">
         <is>
-          <t>Concierge Services</t>
+          <t>Office Support</t>
         </is>
       </c>
       <c r="O982" t="inlineStr">
         <is>
-          <t>DOMUS AL GARHOUD</t>
+          <t>Headoffice</t>
         </is>
       </c>
       <c r="P982" t="inlineStr">
@@ -72294,22 +72280,22 @@
       </c>
       <c r="Q982" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>Riyaz.n</t>
         </is>
       </c>
       <c r="R982" t="inlineStr">
         <is>
-          <t>LPO sent/shared with supplier</t>
+          <t>Procurement Manager</t>
         </is>
       </c>
       <c r="S982" s="5" t="n">
-        <v>46056.5</v>
+        <v>46275.36793981482</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>SCPG-PO2600011</t>
+          <t>SCPG-PO2600002</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -72329,7 +72315,7 @@
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G983" t="inlineStr">
@@ -72343,22 +72329,22 @@
         </is>
       </c>
       <c r="I983" s="5" t="n">
-        <v>46056.5</v>
+        <v>46031.5</v>
       </c>
       <c r="J983" s="5" t="n">
-        <v>46056.5</v>
+        <v>46031.5</v>
       </c>
       <c r="M983" t="n">
-        <v>405</v>
+        <v>2040</v>
       </c>
       <c r="N983" t="inlineStr">
         <is>
-          <t>Building Services</t>
+          <t>Concierge Services</t>
         </is>
       </c>
       <c r="O983" t="inlineStr">
         <is>
-          <t>LE GRAND CHATEAU</t>
+          <t>NORTH RESIDENCE</t>
         </is>
       </c>
       <c r="P983" t="inlineStr">
@@ -72373,34 +72359,37 @@
       </c>
       <c r="R983" t="inlineStr">
         <is>
-          <t>Procurement Manager</t>
-        </is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S983" s="5" t="n">
+        <v>46037.5</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>SCPG-PO2600012</t>
+          <t>SCPG-PO2600004</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>VEND-01072</t>
+          <t>VEND-00224</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>VEND-01072</t>
+          <t>VEND-00224</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>Teclogia General Trading CO LLC</t>
+          <t>Asaleeb Technology</t>
         </is>
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G984" t="inlineStr">
@@ -72414,22 +72403,22 @@
         </is>
       </c>
       <c r="I984" s="5" t="n">
-        <v>46070.5</v>
+        <v>46042.5</v>
       </c>
       <c r="J984" s="5" t="n">
-        <v>46070.5</v>
+        <v>46042.5</v>
       </c>
       <c r="M984" t="n">
-        <v>5295</v>
+        <v>2040</v>
       </c>
       <c r="N984" t="inlineStr">
         <is>
-          <t>Building Services</t>
+          <t>Accomodation Services</t>
         </is>
       </c>
       <c r="O984" t="inlineStr">
         <is>
-          <t>THE PAD BY OMNIYAT</t>
+          <t>Al Rams</t>
         </is>
       </c>
       <c r="P984" t="inlineStr">
@@ -72444,29 +72433,32 @@
       </c>
       <c r="R984" t="inlineStr">
         <is>
-          <t>Procurement Manager</t>
-        </is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S984" s="5" t="n">
+        <v>46048.5</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>SCPG-PO2600014</t>
+          <t>SCPG-PO2600005</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-02528</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-02528</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>Arasca Medical Equipment Trading LLC</t>
+          <t>AL JABER SECURITY COMPANY L.L.C</t>
         </is>
       </c>
       <c r="F985" t="inlineStr">
@@ -72476,7 +72468,7 @@
       </c>
       <c r="G985" t="inlineStr">
         <is>
-          <t>Backorder</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="H985" t="inlineStr">
@@ -72485,13 +72477,13 @@
         </is>
       </c>
       <c r="I985" s="5" t="n">
-        <v>46105.5</v>
+        <v>46048.5</v>
       </c>
       <c r="J985" s="5" t="n">
-        <v>46105.5</v>
+        <v>46048.5</v>
       </c>
       <c r="M985" t="n">
-        <v>970.9299999999999</v>
+        <v>52800</v>
       </c>
       <c r="N985" t="inlineStr">
         <is>
@@ -72500,7 +72492,7 @@
       </c>
       <c r="O985" t="inlineStr">
         <is>
-          <t>WILTON PARK RESIDENCES</t>
+          <t>AL layyah</t>
         </is>
       </c>
       <c r="P985" t="inlineStr">
@@ -72519,33 +72511,33 @@
         </is>
       </c>
       <c r="S985" s="5" t="n">
-        <v>46112.5</v>
+        <v>46080.5</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>SCPG-PO2600037</t>
+          <t>SCPG-PO2600006</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-00465</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-00465</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
+          <t>Fouress (Middle East) Safety Products FZC</t>
         </is>
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G986" t="inlineStr">
@@ -72559,22 +72551,22 @@
         </is>
       </c>
       <c r="I986" s="5" t="n">
-        <v>46119.5</v>
+        <v>46050.5</v>
       </c>
       <c r="J986" s="5" t="n">
-        <v>46119.5</v>
+        <v>46050.5</v>
       </c>
       <c r="M986" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="N986" t="inlineStr">
         <is>
-          <t>Building Services</t>
+          <t>Security Services</t>
         </is>
       </c>
       <c r="O986" t="inlineStr">
         <is>
-          <t>NORTH RESIDENCE</t>
+          <t>THE CREEKSIDE MGALLERY HOTEL</t>
         </is>
       </c>
       <c r="P986" t="inlineStr">
@@ -72589,29 +72581,32 @@
       </c>
       <c r="R986" t="inlineStr">
         <is>
-          <t>Procurement Manager</t>
-        </is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S986" s="5" t="n">
+        <v>46052.5</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>SCPG-PO2600039</t>
+          <t>SCPG-PO2600009</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-00224</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-00224</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>Arasca Medical Equipment Trading LLC</t>
+          <t>Asaleeb Technology</t>
         </is>
       </c>
       <c r="F987" t="inlineStr">
@@ -72630,22 +72625,22 @@
         </is>
       </c>
       <c r="I987" s="5" t="n">
-        <v>46132.5</v>
+        <v>46052.5</v>
       </c>
       <c r="J987" s="5" t="n">
-        <v>46132.5</v>
+        <v>46052.5</v>
       </c>
       <c r="M987" t="n">
-        <v>716.59</v>
+        <v>1170</v>
       </c>
       <c r="N987" t="inlineStr">
         <is>
-          <t>Security Services</t>
+          <t>Concierge Services</t>
         </is>
       </c>
       <c r="O987" t="inlineStr">
         <is>
-          <t>FORTUNATO</t>
+          <t>DOMUS AL GARHOUD</t>
         </is>
       </c>
       <c r="P987" t="inlineStr">
@@ -72664,33 +72659,33 @@
         </is>
       </c>
       <c r="S987" s="5" t="n">
-        <v>46134.5</v>
+        <v>46056.5</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>SCPG-PO2600040</t>
+          <t>SCPG-PO2600011</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-00224</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-00224</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>Arasca Medical Equipment Trading LLC</t>
+          <t>Asaleeb Technology</t>
         </is>
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Draft</t>
         </is>
       </c>
       <c r="G988" t="inlineStr">
@@ -72704,22 +72699,22 @@
         </is>
       </c>
       <c r="I988" s="5" t="n">
-        <v>46132.5</v>
+        <v>46056.5</v>
       </c>
       <c r="J988" s="5" t="n">
-        <v>46132.5</v>
+        <v>46056.5</v>
       </c>
       <c r="M988" t="n">
-        <v>716.59</v>
+        <v>405</v>
       </c>
       <c r="N988" t="inlineStr">
         <is>
-          <t>Security Services</t>
+          <t>Building Services</t>
         </is>
       </c>
       <c r="O988" t="inlineStr">
         <is>
-          <t>SPARKLE TOWERS</t>
+          <t>LE GRAND CHATEAU</t>
         </is>
       </c>
       <c r="P988" t="inlineStr">
@@ -72734,37 +72729,34 @@
       </c>
       <c r="R988" t="inlineStr">
         <is>
-          <t>LPO sent/shared with supplier</t>
-        </is>
-      </c>
-      <c r="S988" s="5" t="n">
-        <v>46134.5</v>
+          <t>Procurement Manager</t>
+        </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>SCPG-PO2600041</t>
+          <t>SCPG-PO2600012</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-01072</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-01072</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>Arasca Medical Equipment Trading LLC</t>
+          <t>Teclogia General Trading CO LLC</t>
         </is>
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Draft</t>
         </is>
       </c>
       <c r="G989" t="inlineStr">
@@ -72778,22 +72770,22 @@
         </is>
       </c>
       <c r="I989" s="5" t="n">
-        <v>46132.5</v>
+        <v>46070.5</v>
       </c>
       <c r="J989" s="5" t="n">
-        <v>46132.5</v>
+        <v>46070.5</v>
       </c>
       <c r="M989" t="n">
-        <v>716.59</v>
+        <v>5295</v>
       </c>
       <c r="N989" t="inlineStr">
         <is>
-          <t>Security Services</t>
+          <t>Building Services</t>
         </is>
       </c>
       <c r="O989" t="inlineStr">
         <is>
-          <t>SHORELINE 7AND8</t>
+          <t>THE PAD BY OMNIYAT</t>
         </is>
       </c>
       <c r="P989" t="inlineStr">
@@ -72808,17 +72800,14 @@
       </c>
       <c r="R989" t="inlineStr">
         <is>
-          <t>LPO sent/shared with supplier</t>
-        </is>
-      </c>
-      <c r="S989" s="5" t="n">
-        <v>46134.5</v>
+          <t>Procurement Manager</t>
+        </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>SCPG-PO2600042</t>
+          <t>SCPG-PO2600014</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
@@ -72852,22 +72841,22 @@
         </is>
       </c>
       <c r="I990" s="5" t="n">
-        <v>46132.5</v>
+        <v>46105.5</v>
       </c>
       <c r="J990" s="5" t="n">
-        <v>46132.5</v>
+        <v>46105.5</v>
       </c>
       <c r="M990" t="n">
-        <v>1175.97</v>
+        <v>970.9299999999999</v>
       </c>
       <c r="N990" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Security Services</t>
         </is>
       </c>
       <c r="O990" t="inlineStr">
         <is>
-          <t>BALQIS RESIDENCE</t>
+          <t>WILTON PARK RESIDENCES</t>
         </is>
       </c>
       <c r="P990" t="inlineStr">
@@ -72886,33 +72875,33 @@
         </is>
       </c>
       <c r="S990" s="5" t="n">
-        <v>46134.5</v>
+        <v>46112.5</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>SCPG-PO2600043</t>
+          <t>SCPG-PO2600037</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-01331</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-01331</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>Arasca Medical Equipment Trading LLC</t>
+          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Draft</t>
         </is>
       </c>
       <c r="G991" t="inlineStr">
@@ -72926,22 +72915,22 @@
         </is>
       </c>
       <c r="I991" s="5" t="n">
-        <v>46132.5</v>
+        <v>46119.5</v>
       </c>
       <c r="J991" s="5" t="n">
-        <v>46132.5</v>
+        <v>46119.5</v>
       </c>
       <c r="M991" t="n">
-        <v>1064.09</v>
+        <v>175</v>
       </c>
       <c r="N991" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Building Services</t>
         </is>
       </c>
       <c r="O991" t="inlineStr">
         <is>
-          <t>SOUTH RESIDENCE</t>
+          <t>NORTH RESIDENCE</t>
         </is>
       </c>
       <c r="P991" t="inlineStr">
@@ -72956,17 +72945,14 @@
       </c>
       <c r="R991" t="inlineStr">
         <is>
-          <t>LPO sent/shared with supplier</t>
-        </is>
-      </c>
-      <c r="S991" s="5" t="n">
-        <v>46134.5</v>
+          <t>Procurement Manager</t>
+        </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>SCPG-PO2600044</t>
+          <t>SCPG-PO2600039</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
@@ -73006,16 +72992,16 @@
         <v>46132.5</v>
       </c>
       <c r="M992" t="n">
-        <v>1025.45</v>
+        <v>716.59</v>
       </c>
       <c r="N992" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Security Services</t>
         </is>
       </c>
       <c r="O992" t="inlineStr">
         <is>
-          <t>MAG 318</t>
+          <t>FORTUNATO</t>
         </is>
       </c>
       <c r="P992" t="inlineStr">
@@ -73040,7 +73026,7 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>SCPG-PO2600045</t>
+          <t>SCPG-PO2600040</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -73080,16 +73066,16 @@
         <v>46132.5</v>
       </c>
       <c r="M993" t="n">
-        <v>743.52</v>
+        <v>716.59</v>
       </c>
       <c r="N993" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Security Services</t>
         </is>
       </c>
       <c r="O993" t="inlineStr">
         <is>
-          <t>THE AUTOGRAPH</t>
+          <t>SPARKLE TOWERS</t>
         </is>
       </c>
       <c r="P993" t="inlineStr">
@@ -73114,7 +73100,7 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>SCPG-PO2600058</t>
+          <t>SCPG-PO2600041</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
@@ -73148,13 +73134,13 @@
         </is>
       </c>
       <c r="I994" s="5" t="n">
-        <v>46136.5</v>
+        <v>46132.5</v>
       </c>
       <c r="J994" s="5" t="n">
-        <v>46136.5</v>
+        <v>46132.5</v>
       </c>
       <c r="M994" t="n">
-        <v>439.6</v>
+        <v>716.59</v>
       </c>
       <c r="N994" t="inlineStr">
         <is>
@@ -73163,7 +73149,7 @@
       </c>
       <c r="O994" t="inlineStr">
         <is>
-          <t>VISTA BY PRESTIGE ONE</t>
+          <t>SHORELINE 7AND8</t>
         </is>
       </c>
       <c r="P994" t="inlineStr">
@@ -73182,28 +73168,28 @@
         </is>
       </c>
       <c r="S994" s="5" t="n">
-        <v>46167.5</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>SCPG-PO2600059</t>
+          <t>SCPG-PO2600042</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
+          <t>Arasca Medical Equipment Trading LLC</t>
         </is>
       </c>
       <c r="F995" t="inlineStr">
@@ -73213,7 +73199,7 @@
       </c>
       <c r="G995" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Backorder</t>
         </is>
       </c>
       <c r="H995" t="inlineStr">
@@ -73222,22 +73208,22 @@
         </is>
       </c>
       <c r="I995" s="5" t="n">
-        <v>46146.5</v>
+        <v>46132.5</v>
       </c>
       <c r="J995" s="5" t="n">
-        <v>46146.5</v>
+        <v>46132.5</v>
       </c>
       <c r="M995" t="n">
-        <v>1456</v>
+        <v>1175.97</v>
       </c>
       <c r="N995" t="inlineStr">
         <is>
-          <t>Concierge Services</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="O995" t="inlineStr">
         <is>
-          <t>BEACH WALK 1 BY IMTIAZ</t>
+          <t>BALQIS RESIDENCE</t>
         </is>
       </c>
       <c r="P995" t="inlineStr">
@@ -73256,28 +73242,28 @@
         </is>
       </c>
       <c r="S995" s="5" t="n">
-        <v>46210.5</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>SCPG-PO2600061</t>
+          <t>SCPG-PO2600043</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>VEND-00340</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>VEND-00340</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>CROWNS SECURITY SERVICES L.L.C</t>
+          <t>Arasca Medical Equipment Trading LLC</t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
@@ -73287,7 +73273,7 @@
       </c>
       <c r="G996" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Backorder</t>
         </is>
       </c>
       <c r="H996" t="inlineStr">
@@ -73296,22 +73282,22 @@
         </is>
       </c>
       <c r="I996" s="5" t="n">
-        <v>46167.5</v>
+        <v>46132.5</v>
       </c>
       <c r="J996" s="5" t="n">
-        <v>46167.5</v>
+        <v>46132.5</v>
       </c>
       <c r="M996" t="n">
-        <v>72000</v>
+        <v>1064.09</v>
       </c>
       <c r="N996" t="inlineStr">
         <is>
-          <t>Concierge Services</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="O996" t="inlineStr">
         <is>
-          <t>DOMUS INDIGO</t>
+          <t>SOUTH RESIDENCE</t>
         </is>
       </c>
       <c r="P996" t="inlineStr">
@@ -73330,28 +73316,28 @@
         </is>
       </c>
       <c r="S996" s="5" t="n">
-        <v>1.5</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>SCPG-PO2600062</t>
+          <t>SCPG-PO2600044</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>VEND-00207</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>VEND-00207</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>Apex Professional Security Services LLC</t>
+          <t>Arasca Medical Equipment Trading LLC</t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
@@ -73361,7 +73347,7 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Backorder</t>
         </is>
       </c>
       <c r="H997" t="inlineStr">
@@ -73370,22 +73356,22 @@
         </is>
       </c>
       <c r="I997" s="5" t="n">
-        <v>46190.5</v>
+        <v>46132.5</v>
       </c>
       <c r="J997" s="5" t="n">
-        <v>46190.5</v>
+        <v>46132.5</v>
       </c>
       <c r="M997" t="n">
-        <v>795000</v>
+        <v>1025.45</v>
       </c>
       <c r="N997" t="inlineStr">
         <is>
-          <t>Security Services</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="O997" t="inlineStr">
         <is>
-          <t>QUEUE POINT</t>
+          <t>MAG 318</t>
         </is>
       </c>
       <c r="P997" t="inlineStr">
@@ -73404,28 +73390,28 @@
         </is>
       </c>
       <c r="S997" s="5" t="n">
-        <v>46203.5</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>SCPG-PO2600063</t>
+          <t>SCPG-PO2600045</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
+          <t>Arasca Medical Equipment Trading LLC</t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
@@ -73444,22 +73430,22 @@
         </is>
       </c>
       <c r="I998" s="5" t="n">
-        <v>46192.5</v>
+        <v>46132.5</v>
       </c>
       <c r="J998" s="5" t="n">
-        <v>46192.5</v>
+        <v>46132.5</v>
       </c>
       <c r="M998" t="n">
-        <v>306</v>
+        <v>743.52</v>
       </c>
       <c r="N998" t="inlineStr">
         <is>
-          <t>Concierge Services</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="O998" t="inlineStr">
         <is>
-          <t>THE8</t>
+          <t>THE AUTOGRAPH</t>
         </is>
       </c>
       <c r="P998" t="inlineStr">
@@ -73478,28 +73464,28 @@
         </is>
       </c>
       <c r="S998" s="5" t="n">
-        <v>46198.5</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>SCPG-PO2600065</t>
+          <t>SCPG-PO2600058</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-00216</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
+          <t>Arasca Medical Equipment Trading LLC</t>
         </is>
       </c>
       <c r="F999" t="inlineStr">
@@ -73518,22 +73504,22 @@
         </is>
       </c>
       <c r="I999" s="5" t="n">
-        <v>46204.5</v>
+        <v>46136.5</v>
       </c>
       <c r="J999" s="5" t="n">
-        <v>46204.5</v>
+        <v>46136.5</v>
       </c>
       <c r="M999" t="n">
-        <v>350</v>
+        <v>439.6</v>
       </c>
       <c r="N999" t="inlineStr">
         <is>
-          <t>Contracted Cleaning Services</t>
+          <t>Security Services</t>
         </is>
       </c>
       <c r="O999" t="inlineStr">
         <is>
-          <t>MAG 318</t>
+          <t>VISTA BY PRESTIGE ONE</t>
         </is>
       </c>
       <c r="P999" t="inlineStr">
@@ -73552,28 +73538,28 @@
         </is>
       </c>
       <c r="S999" s="5" t="n">
-        <v>46220.5</v>
+        <v>46167.5</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>SCPG-PO2600066</t>
+          <t>SCPG-PO2600059</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>VEND-02675</t>
+          <t>VEND-01331</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>VEND-02675</t>
+          <t>VEND-01331</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>GULF GLOBAL RESOURCES L.L.C</t>
+          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
@@ -73583,7 +73569,7 @@
       </c>
       <c r="G1000" t="inlineStr">
         <is>
-          <t>Backorder</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="H1000" t="inlineStr">
@@ -73592,13 +73578,13 @@
         </is>
       </c>
       <c r="I1000" s="5" t="n">
-        <v>46209.5</v>
+        <v>46146.5</v>
       </c>
       <c r="J1000" s="5" t="n">
-        <v>46209.5</v>
+        <v>46146.5</v>
       </c>
       <c r="M1000" t="n">
-        <v>153</v>
+        <v>1456</v>
       </c>
       <c r="N1000" t="inlineStr">
         <is>
@@ -73607,7 +73593,7 @@
       </c>
       <c r="O1000" t="inlineStr">
         <is>
-          <t>DOMUS INDIGO</t>
+          <t>BEACH WALK 1 BY IMTIAZ</t>
         </is>
       </c>
       <c r="P1000" t="inlineStr">
@@ -73626,28 +73612,28 @@
         </is>
       </c>
       <c r="S1000" s="5" t="n">
-        <v>46213.5</v>
+        <v>46210.5</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>SCPG-PO2600067</t>
+          <t>SCPG-PO2600061</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>VEND-02675</t>
+          <t>VEND-00340</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>VEND-02675</t>
+          <t>VEND-00340</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>GULF GLOBAL RESOURCES L.L.C</t>
+          <t>CROWNS SECURITY SERVICES L.L.C</t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
@@ -73657,7 +73643,7 @@
       </c>
       <c r="G1001" t="inlineStr">
         <is>
-          <t>Backorder</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="H1001" t="inlineStr">
@@ -73666,13 +73652,13 @@
         </is>
       </c>
       <c r="I1001" s="5" t="n">
-        <v>46209.5</v>
+        <v>46167.5</v>
       </c>
       <c r="J1001" s="5" t="n">
-        <v>46209.5</v>
+        <v>46167.5</v>
       </c>
       <c r="M1001" t="n">
-        <v>255</v>
+        <v>72000</v>
       </c>
       <c r="N1001" t="inlineStr">
         <is>
@@ -73681,7 +73667,7 @@
       </c>
       <c r="O1001" t="inlineStr">
         <is>
-          <t>THE OPUS BY OMNIYAT</t>
+          <t>DOMUS INDIGO</t>
         </is>
       </c>
       <c r="P1001" t="inlineStr">
@@ -73700,28 +73686,28 @@
         </is>
       </c>
       <c r="S1001" s="5" t="n">
-        <v>46210.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>SCPG-PO2600068</t>
+          <t>SCPG-PO2600062</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>VEND-01125</t>
+          <t>VEND-00207</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>VEND-01125</t>
+          <t>VEND-00207</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>AMAN SECURITY AND GUARD SYSTEMS CO LLC</t>
+          <t>Apex Professional Security Services LLC</t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
@@ -73740,13 +73726,13 @@
         </is>
       </c>
       <c r="I1002" s="5" t="n">
-        <v>46218.5</v>
+        <v>46190.5</v>
       </c>
       <c r="J1002" s="5" t="n">
-        <v>46218.5</v>
+        <v>46190.5</v>
       </c>
       <c r="M1002" t="n">
-        <v>663000</v>
+        <v>795000</v>
       </c>
       <c r="N1002" t="inlineStr">
         <is>
@@ -73755,7 +73741,7 @@
       </c>
       <c r="O1002" t="inlineStr">
         <is>
-          <t>AL TAY HILLS</t>
+          <t>QUEUE POINT</t>
         </is>
       </c>
       <c r="P1002" t="inlineStr">
@@ -73774,13 +73760,13 @@
         </is>
       </c>
       <c r="S1002" s="5" t="n">
-        <v>46240.5</v>
+        <v>46203.5</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>SCPG-PO2600069</t>
+          <t>SCPG-PO2600063</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -73814,13 +73800,13 @@
         </is>
       </c>
       <c r="I1003" s="5" t="n">
-        <v>46219.5</v>
+        <v>46192.5</v>
       </c>
       <c r="J1003" s="5" t="n">
-        <v>46219.5</v>
+        <v>46192.5</v>
       </c>
       <c r="M1003" t="n">
-        <v>196</v>
+        <v>306</v>
       </c>
       <c r="N1003" t="inlineStr">
         <is>
@@ -73829,7 +73815,7 @@
       </c>
       <c r="O1003" t="inlineStr">
         <is>
-          <t>DOMUS AL GARHOUD</t>
+          <t>THE8</t>
         </is>
       </c>
       <c r="P1003" t="inlineStr">
@@ -73848,13 +73834,13 @@
         </is>
       </c>
       <c r="S1003" s="5" t="n">
-        <v>46220.5</v>
+        <v>46198.5</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>SCPG-PO2600070</t>
+          <t>SCPG-PO2600065</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
@@ -73888,22 +73874,22 @@
         </is>
       </c>
       <c r="I1004" s="5" t="n">
-        <v>46224.5</v>
+        <v>46204.5</v>
       </c>
       <c r="J1004" s="5" t="n">
-        <v>46224.5</v>
+        <v>46204.5</v>
       </c>
       <c r="M1004" t="n">
-        <v>580</v>
+        <v>350</v>
       </c>
       <c r="N1004" t="inlineStr">
         <is>
-          <t>Security Services</t>
+          <t>Contracted Cleaning Services</t>
         </is>
       </c>
       <c r="O1004" t="inlineStr">
         <is>
-          <t>BEACH WALK 1 BY IMTIAZ</t>
+          <t>MAG 318</t>
         </is>
       </c>
       <c r="P1004" t="inlineStr">
@@ -73922,28 +73908,28 @@
         </is>
       </c>
       <c r="S1004" s="5" t="n">
-        <v>46226.5</v>
+        <v>46220.5</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>SCPG-PO2600071</t>
+          <t>SCPG-PO2600066</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-02675</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-02675</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
+          <t>GULF GLOBAL RESOURCES L.L.C</t>
         </is>
       </c>
       <c r="F1005" t="inlineStr">
@@ -73962,22 +73948,22 @@
         </is>
       </c>
       <c r="I1005" s="5" t="n">
-        <v>46224.5</v>
+        <v>46209.5</v>
       </c>
       <c r="J1005" s="5" t="n">
-        <v>46224.5</v>
+        <v>46209.5</v>
       </c>
       <c r="M1005" t="n">
-        <v>435</v>
+        <v>153</v>
       </c>
       <c r="N1005" t="inlineStr">
         <is>
-          <t>Security Services</t>
+          <t>Concierge Services</t>
         </is>
       </c>
       <c r="O1005" t="inlineStr">
         <is>
-          <t>VISTA BY PRESTIGE ONE</t>
+          <t>DOMUS INDIGO</t>
         </is>
       </c>
       <c r="P1005" t="inlineStr">
@@ -73996,28 +73982,28 @@
         </is>
       </c>
       <c r="S1005" s="5" t="n">
-        <v>46226.5</v>
+        <v>46213.5</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>SCPG-PO2600072</t>
+          <t>SCPG-PO2600067</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-02675</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>VEND-01331</t>
+          <t>VEND-02675</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
+          <t>GULF GLOBAL RESOURCES L.L.C</t>
         </is>
       </c>
       <c r="F1006" t="inlineStr">
@@ -74036,22 +74022,22 @@
         </is>
       </c>
       <c r="I1006" s="5" t="n">
-        <v>46224.5</v>
+        <v>46209.5</v>
       </c>
       <c r="J1006" s="5" t="n">
-        <v>46224.5</v>
+        <v>46209.5</v>
       </c>
       <c r="M1006" t="n">
-        <v>636</v>
+        <v>255</v>
       </c>
       <c r="N1006" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Concierge Services</t>
         </is>
       </c>
       <c r="O1006" t="inlineStr">
         <is>
-          <t>BEACH WALK 1 BY IMTIAZ</t>
+          <t>THE OPUS BY OMNIYAT</t>
         </is>
       </c>
       <c r="P1006" t="inlineStr">
@@ -74070,28 +74056,28 @@
         </is>
       </c>
       <c r="S1006" s="5" t="n">
-        <v>46226.5</v>
+        <v>46210.5</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>SCPG-PO2600073</t>
+          <t>SCPG-PO2600068</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>VEND-02528</t>
+          <t>VEND-01125</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>VEND-02528</t>
+          <t>VEND-01125</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>AL JABER SECURITY COMPANY L.L.C</t>
+          <t>AMAN SECURITY AND GUARD SYSTEMS CO LLC</t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
@@ -74110,13 +74096,13 @@
         </is>
       </c>
       <c r="I1007" s="5" t="n">
-        <v>46239.5</v>
+        <v>46218.5</v>
       </c>
       <c r="J1007" s="5" t="n">
-        <v>46239.5</v>
+        <v>46218.5</v>
       </c>
       <c r="M1007" t="n">
-        <v>52800</v>
+        <v>663000</v>
       </c>
       <c r="N1007" t="inlineStr">
         <is>
@@ -74125,7 +74111,7 @@
       </c>
       <c r="O1007" t="inlineStr">
         <is>
-          <t>AL layyah</t>
+          <t>AL TAY HILLS</t>
         </is>
       </c>
       <c r="P1007" t="inlineStr">
@@ -74144,28 +74130,28 @@
         </is>
       </c>
       <c r="S1007" s="5" t="n">
-        <v>46244.5</v>
+        <v>46240.5</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>SCPG-PO2600075</t>
+          <t>SCPG-PO2600069</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-01331</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>VEND-00216</t>
+          <t>VEND-01331</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>Arasca Medical Equipment Trading LLC</t>
+          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
         </is>
       </c>
       <c r="F1008" t="inlineStr">
@@ -74184,22 +74170,22 @@
         </is>
       </c>
       <c r="I1008" s="5" t="n">
-        <v>46251.5</v>
+        <v>46219.5</v>
       </c>
       <c r="J1008" s="5" t="n">
-        <v>46251.5</v>
+        <v>46219.5</v>
       </c>
       <c r="M1008" t="n">
-        <v>561.1900000000001</v>
+        <v>196</v>
       </c>
       <c r="N1008" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Concierge Services</t>
         </is>
       </c>
       <c r="O1008" t="inlineStr">
         <is>
-          <t>BEACH WALK 1 BY IMTIAZ</t>
+          <t>DOMUS AL GARHOUD</t>
         </is>
       </c>
       <c r="P1008" t="inlineStr">
@@ -74218,13 +74204,13 @@
         </is>
       </c>
       <c r="S1008" s="5" t="n">
-        <v>46266.5</v>
+        <v>46220.5</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>SCPG-PO2600076</t>
+          <t>SCPG-PO2600070</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -74258,13 +74244,13 @@
         </is>
       </c>
       <c r="I1009" s="5" t="n">
-        <v>46260.5</v>
+        <v>46224.5</v>
       </c>
       <c r="J1009" s="5" t="n">
-        <v>46260.5</v>
+        <v>46224.5</v>
       </c>
       <c r="M1009" t="n">
-        <v>318</v>
+        <v>580</v>
       </c>
       <c r="N1009" t="inlineStr">
         <is>
@@ -74273,7 +74259,7 @@
       </c>
       <c r="O1009" t="inlineStr">
         <is>
-          <t>BALQIS RESIDENCE</t>
+          <t>BEACH WALK 1 BY IMTIAZ</t>
         </is>
       </c>
       <c r="P1009" t="inlineStr">
@@ -74292,28 +74278,28 @@
         </is>
       </c>
       <c r="S1009" s="5" t="n">
-        <v>46266.5</v>
+        <v>46226.5</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>SCPG-PO2600077</t>
+          <t>SCPG-PO2600071</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>VEND-00689</t>
+          <t>VEND-01331</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>VEND-00689</t>
+          <t>VEND-01331</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>Microhit Technologies LLC</t>
+          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
         </is>
       </c>
       <c r="F1010" t="inlineStr">
@@ -74332,13 +74318,13 @@
         </is>
       </c>
       <c r="I1010" s="5" t="n">
-        <v>46269.5</v>
+        <v>46224.5</v>
       </c>
       <c r="J1010" s="5" t="n">
-        <v>46269.5</v>
+        <v>46224.5</v>
       </c>
       <c r="M1010" t="n">
-        <v>10965</v>
+        <v>435</v>
       </c>
       <c r="N1010" t="inlineStr">
         <is>
@@ -74347,7 +74333,7 @@
       </c>
       <c r="O1010" t="inlineStr">
         <is>
-          <t>THE8</t>
+          <t>VISTA BY PRESTIGE ONE</t>
         </is>
       </c>
       <c r="P1010" t="inlineStr">
@@ -74366,80 +74352,524 @@
         </is>
       </c>
       <c r="S1010" s="5" t="n">
-        <v>46274.5</v>
+        <v>46226.5</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
+          <t>SCPG-PO2600072</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>VEND-01331</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>VEND-01331</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>Backorder</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="I1011" s="5" t="n">
+        <v>46224.5</v>
+      </c>
+      <c r="J1011" s="5" t="n">
+        <v>46224.5</v>
+      </c>
+      <c r="M1011" t="n">
+        <v>636</v>
+      </c>
+      <c r="N1011" t="inlineStr">
+        <is>
+          <t>Leisure Services</t>
+        </is>
+      </c>
+      <c r="O1011" t="inlineStr">
+        <is>
+          <t>BEACH WALK 1 BY IMTIAZ</t>
+        </is>
+      </c>
+      <c r="P1011" t="inlineStr">
+        <is>
+          <t>Contracted</t>
+        </is>
+      </c>
+      <c r="Q1011" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="R1011" t="inlineStr">
+        <is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S1011" s="5" t="n">
+        <v>46226.5</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>SCPG-PO2600073</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>VEND-02528</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>VEND-02528</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>AL JABER SECURITY COMPANY L.L.C</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="I1012" s="5" t="n">
+        <v>46239.5</v>
+      </c>
+      <c r="J1012" s="5" t="n">
+        <v>46239.5</v>
+      </c>
+      <c r="M1012" t="n">
+        <v>52800</v>
+      </c>
+      <c r="N1012" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="O1012" t="inlineStr">
+        <is>
+          <t>AL layyah</t>
+        </is>
+      </c>
+      <c r="P1012" t="inlineStr">
+        <is>
+          <t>Contracted</t>
+        </is>
+      </c>
+      <c r="Q1012" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="R1012" t="inlineStr">
+        <is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S1012" s="5" t="n">
+        <v>46244.5</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>SCPG-PO2600074</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>VEND-00450</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>VEND-00450</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>FAYAFY SWIMMING POOLS TRADING LLC</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>InReview</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>Backorder</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="I1013" s="5" t="n">
+        <v>46248.5</v>
+      </c>
+      <c r="J1013" s="5" t="n">
+        <v>46248.5</v>
+      </c>
+      <c r="M1013" t="n">
+        <v>5216</v>
+      </c>
+      <c r="N1013" t="inlineStr">
+        <is>
+          <t>Leisure Services</t>
+        </is>
+      </c>
+      <c r="O1013" t="inlineStr">
+        <is>
+          <t>BEACH WALK 1 BY IMTIAZ</t>
+        </is>
+      </c>
+      <c r="P1013" t="inlineStr">
+        <is>
+          <t>Contracted</t>
+        </is>
+      </c>
+      <c r="Q1013" t="inlineStr">
+        <is>
+          <t>Ayman.ismail</t>
+        </is>
+      </c>
+      <c r="R1013" t="inlineStr">
+        <is>
+          <t>Procurement Manager</t>
+        </is>
+      </c>
+      <c r="S1013" s="5" t="n">
+        <v>46275.33657407408</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>SCPG-PO2600075</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>VEND-00216</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>VEND-00216</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Arasca Medical Equipment Trading LLC</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>Backorder</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="I1014" s="5" t="n">
+        <v>46251.5</v>
+      </c>
+      <c r="J1014" s="5" t="n">
+        <v>46251.5</v>
+      </c>
+      <c r="M1014" t="n">
+        <v>561.1900000000001</v>
+      </c>
+      <c r="N1014" t="inlineStr">
+        <is>
+          <t>Leisure Services</t>
+        </is>
+      </c>
+      <c r="O1014" t="inlineStr">
+        <is>
+          <t>BEACH WALK 1 BY IMTIAZ</t>
+        </is>
+      </c>
+      <c r="P1014" t="inlineStr">
+        <is>
+          <t>Contracted</t>
+        </is>
+      </c>
+      <c r="Q1014" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="R1014" t="inlineStr">
+        <is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S1014" s="5" t="n">
+        <v>46266.5</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>SCPG-PO2600076</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>VEND-01331</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>VEND-01331</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>AL MENHA TAILORING AND EMBROIDERY LLC</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>Backorder</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="I1015" s="5" t="n">
+        <v>46260.5</v>
+      </c>
+      <c r="J1015" s="5" t="n">
+        <v>46260.5</v>
+      </c>
+      <c r="M1015" t="n">
+        <v>318</v>
+      </c>
+      <c r="N1015" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="O1015" t="inlineStr">
+        <is>
+          <t>BALQIS RESIDENCE</t>
+        </is>
+      </c>
+      <c r="P1015" t="inlineStr">
+        <is>
+          <t>Contracted</t>
+        </is>
+      </c>
+      <c r="Q1015" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="R1015" t="inlineStr">
+        <is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S1015" s="5" t="n">
+        <v>46266.5</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>SCPG-PO2600077</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>VEND-00689</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>VEND-00689</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Microhit Technologies LLC</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>Backorder</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="I1016" s="5" t="n">
+        <v>46269.5</v>
+      </c>
+      <c r="J1016" s="5" t="n">
+        <v>46269.5</v>
+      </c>
+      <c r="M1016" t="n">
+        <v>10965</v>
+      </c>
+      <c r="N1016" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="O1016" t="inlineStr">
+        <is>
+          <t>THE8</t>
+        </is>
+      </c>
+      <c r="P1016" t="inlineStr">
+        <is>
+          <t>Contracted</t>
+        </is>
+      </c>
+      <c r="Q1016" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="R1016" t="inlineStr">
+        <is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S1016" s="5" t="n">
+        <v>46274.5</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
           <t>SCPG-PO2600078</t>
         </is>
       </c>
-      <c r="B1011" t="inlineStr">
+      <c r="B1017" t="inlineStr">
         <is>
           <t>VEND-00689</t>
         </is>
       </c>
-      <c r="C1011" t="inlineStr">
+      <c r="C1017" t="inlineStr">
         <is>
           <t>VEND-00689</t>
         </is>
       </c>
-      <c r="D1011" t="inlineStr">
+      <c r="D1017" t="inlineStr">
         <is>
           <t>Microhit Technologies LLC</t>
         </is>
       </c>
-      <c r="F1011" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="G1011" t="inlineStr">
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
         <is>
           <t>Backorder</t>
         </is>
       </c>
-      <c r="H1011" t="inlineStr">
-        <is>
-          <t>AED</t>
-        </is>
-      </c>
-      <c r="I1011" s="5" t="n">
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="I1017" s="5" t="n">
         <v>46269.5</v>
       </c>
-      <c r="J1011" s="5" t="n">
+      <c r="J1017" s="5" t="n">
         <v>46269.5</v>
       </c>
-      <c r="M1011" t="n">
+      <c r="M1017" t="n">
         <v>8685</v>
       </c>
-      <c r="N1011" t="inlineStr">
+      <c r="N1017" t="inlineStr">
         <is>
           <t>Security Services</t>
         </is>
       </c>
-      <c r="O1011" t="inlineStr">
+      <c r="O1017" t="inlineStr">
         <is>
           <t>MOVENPICK LAGUNA</t>
         </is>
       </c>
-      <c r="P1011" t="inlineStr">
+      <c r="P1017" t="inlineStr">
         <is>
           <t>Contracted</t>
         </is>
       </c>
-      <c r="Q1011" t="inlineStr">
-        <is>
-          <t>not recorded</t>
-        </is>
-      </c>
-      <c r="R1011" t="inlineStr">
-        <is>
-          <t>LPO sent/shared with supplier</t>
-        </is>
-      </c>
-      <c r="S1011" s="5" t="n">
+      <c r="Q1017" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="R1017" t="inlineStr">
+        <is>
+          <t>LPO sent/shared with supplier</t>
+        </is>
+      </c>
+      <c r="S1017" s="5" t="n">
         <v>46274.5</v>
       </c>
     </row>
